--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -1708,7 +1708,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G7" s="2">
         <v>2</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F8" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2">
         <v>3</v>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F8" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G8" s="2">
         <v>3</v>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="属性奖励" sheetId="1" r:id="rId1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="145">
   <si>
     <t>#</t>
   </si>
@@ -431,7 +431,7 @@
     <t>4000,4</t>
   </si>
   <si>
-    <t>杀怪概率获取</t>
+    <t>击杀小怪概率获取</t>
   </si>
   <si>
     <t>增加血量</t>
@@ -482,6 +482,9 @@
     <t>21,93</t>
   </si>
   <si>
+    <t>击杀区域BOSS概率获取</t>
+  </si>
+  <si>
     <t>增加暴击</t>
   </si>
   <si>
@@ -510,6 +513,78 @@
   </si>
   <si>
     <t>增加闪避</t>
+  </si>
+  <si>
+    <t>保护脆皮Ⅱ</t>
+  </si>
+  <si>
+    <t>1001,2001</t>
+  </si>
+  <si>
+    <t>击杀困难小怪概率获取</t>
+  </si>
+  <si>
+    <t>我要输出Ⅱ</t>
+  </si>
+  <si>
+    <t>1002,2002</t>
+  </si>
+  <si>
+    <t>我不想死Ⅱ</t>
+  </si>
+  <si>
+    <t>1003,2003</t>
+  </si>
+  <si>
+    <t>给点钱把Ⅱ</t>
+  </si>
+  <si>
+    <t>85,93</t>
+  </si>
+  <si>
+    <t>我想升级Ⅱ</t>
+  </si>
+  <si>
+    <t>86,93</t>
+  </si>
+  <si>
+    <t>狠狠的暴打</t>
+  </si>
+  <si>
+    <t>伤害加成</t>
+  </si>
+  <si>
+    <t>我要打一百个</t>
+  </si>
+  <si>
+    <t>击杀困难区域BOSS概率获取</t>
+  </si>
+  <si>
+    <t>真的血牛</t>
+  </si>
+  <si>
+    <t>10001,93</t>
+  </si>
+  <si>
+    <t>生命倍率</t>
+  </si>
+  <si>
+    <t>真的肉盾</t>
+  </si>
+  <si>
+    <t>10002,93</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>真的输出</t>
+  </si>
+  <si>
+    <t>10003,93</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
   </si>
   <si>
     <t>传奇人生</t>
@@ -2489,7 +2564,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P21"/>
+  <dimension ref="C1:P31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -2500,7 +2575,7 @@
     <col min="12" max="12" width="13.9090909090909" style="2" customWidth="1"/>
     <col min="13" max="13" width="13.7272727272727" style="2" customWidth="1"/>
     <col min="14" max="14" width="16.6363636363636" style="2" customWidth="1"/>
-    <col min="15" max="15" width="22.2727272727273" style="2" customWidth="1"/>
+    <col min="15" max="15" width="26.9090909090909" style="2" customWidth="1"/>
     <col min="16" max="16" width="21" style="2" customWidth="1"/>
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
@@ -2901,10 +2976,10 @@
         <v>20</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2915,7 +2990,7 @@
         <v>501</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F12" s="2">
         <v>20</v>
@@ -2936,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>20</v>
@@ -2945,10 +3020,10 @@
         <v>20</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2959,7 +3034,7 @@
         <v>501</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F13" s="2">
         <v>10</v>
@@ -2980,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>20</v>
@@ -2989,10 +3064,10 @@
         <v>20</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3003,7 +3078,7 @@
         <v>501</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
@@ -3024,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>20</v>
@@ -3033,142 +3108,686 @@
         <v>20</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C16" s="2">
+        <v>50010</v>
+      </c>
+      <c r="D16" s="2">
+        <v>503</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="2">
+        <v>20</v>
+      </c>
+      <c r="G16" s="2">
+        <v>10003</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C17" s="2">
+        <v>50011</v>
+      </c>
+      <c r="D17" s="2">
+        <v>503</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="2">
+        <v>20</v>
+      </c>
+      <c r="G17" s="2">
+        <v>10003</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C18" s="2">
+        <v>50012</v>
+      </c>
+      <c r="D18" s="2">
+        <v>503</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="2">
+        <v>20</v>
+      </c>
+      <c r="G18" s="2">
+        <v>10003</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C19" s="2">
+        <v>50013</v>
+      </c>
+      <c r="D19" s="2">
+        <v>503</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="2">
+        <v>20</v>
+      </c>
+      <c r="G19" s="2">
+        <v>10003</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C20" s="2">
+        <v>50014</v>
+      </c>
+      <c r="D20" s="2">
+        <v>503</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="2">
+        <v>20</v>
+      </c>
+      <c r="G20" s="2">
+        <v>10003</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C21" s="2">
+        <v>50015</v>
+      </c>
+      <c r="D21" s="2">
+        <v>503</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" s="2">
+        <v>20</v>
+      </c>
+      <c r="G21" s="2">
+        <v>10003</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C22" s="2">
+        <v>50016</v>
+      </c>
+      <c r="D22" s="2">
+        <v>503</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" s="2">
+        <v>40</v>
+      </c>
+      <c r="G22" s="2">
+        <v>10003</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C23" s="2">
+        <v>50017</v>
+      </c>
+      <c r="D23" s="2">
+        <v>503</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" s="2">
+        <v>10004</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C24" s="2">
+        <v>50018</v>
+      </c>
+      <c r="D24" s="2">
+        <v>503</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" s="2">
+        <v>15</v>
+      </c>
+      <c r="G24" s="2">
+        <v>10004</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C25" s="2">
+        <v>50019</v>
+      </c>
+      <c r="D25" s="2">
+        <v>503</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="2">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2">
+        <v>10004</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C26" s="2">
+        <v>50020</v>
+      </c>
+      <c r="D26" s="2">
+        <v>503</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2">
+        <v>10004</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C27" s="2">
+        <v>50021</v>
+      </c>
+      <c r="D27" s="2">
+        <v>503</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" s="2">
+        <v>5</v>
+      </c>
+      <c r="G27" s="2">
+        <v>10004</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C29" s="2">
         <v>52001</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D29" s="2">
         <v>502</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
-      <c r="L19" s="5" t="s">
+      <c r="E29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="L29" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="M19" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="N19" s="5" t="s">
+      <c r="M29" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="N29" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="O19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:16">
-      <c r="C20" s="2">
+      <c r="O29" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:16">
+      <c r="C30" s="2">
         <v>52002</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D30" s="2">
         <v>502</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
-        <v>0</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1</v>
-      </c>
-      <c r="L20" s="5" t="s">
+      <c r="E30" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
+      <c r="L30" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="M20" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="N20" s="5" t="s">
+      <c r="M30" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="N30" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="O20" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:16">
-      <c r="C21" s="2">
+      <c r="O30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:16">
+      <c r="C31" s="2">
         <v>52003</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D31" s="2">
         <v>502</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2">
-        <v>1</v>
-      </c>
-      <c r="L21" s="5" t="s">
+      <c r="E31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
+      <c r="L31" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="M21" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="N21" s="5" t="s">
+      <c r="M31" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="N31" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="O21" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>119</v>
+      <c r="O31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="148">
   <si>
     <t>#</t>
   </si>
@@ -552,6 +552,15 @@
   </si>
   <si>
     <t>伤害加成</t>
+  </si>
+  <si>
+    <t>死死的抵抗</t>
+  </si>
+  <si>
+    <t>28,93</t>
+  </si>
+  <si>
+    <t>减伤加成</t>
   </si>
   <si>
     <t>我要打一百个</t>
@@ -2564,7 +2573,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P31"/>
+  <dimension ref="C1:P32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -3363,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>20</v>
@@ -3389,7 +3398,7 @@
         <v>124</v>
       </c>
       <c r="F22" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G22" s="2">
         <v>10003</v>
@@ -3407,7 +3416,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>20</v>
@@ -3419,7 +3428,7 @@
         <v>113</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3430,13 +3439,13 @@
         <v>503</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F23" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G23" s="2">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
@@ -3451,7 +3460,7 @@
         <v>1</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M23" s="5" t="s">
         <v>20</v>
@@ -3460,10 +3469,10 @@
         <v>20</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3474,7 +3483,7 @@
         <v>503</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F24" s="2">
         <v>15</v>
@@ -3495,7 +3504,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>20</v>
@@ -3504,13 +3513,13 @@
         <v>20</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" customHeight="1" spans="3:16">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C25" s="2">
         <v>50019</v>
       </c>
@@ -3518,10 +3527,10 @@
         <v>503</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F25" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25" s="2">
         <v>10004</v>
@@ -3539,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>20</v>
@@ -3548,10 +3557,10 @@
         <v>20</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" customFormat="1" customHeight="1" spans="3:16">
@@ -3592,7 +3601,7 @@
         <v>20</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>131</v>
@@ -3609,7 +3618,7 @@
         <v>132</v>
       </c>
       <c r="F27" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G27" s="2">
         <v>10004</v>
@@ -3636,111 +3645,111 @@
         <v>20</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C29" s="2">
+      <c r="C28" s="2">
+        <v>50022</v>
+      </c>
+      <c r="D28" s="2">
+        <v>503</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5</v>
+      </c>
+      <c r="G28" s="2">
+        <v>10004</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C30" s="2">
         <v>52001</v>
-      </c>
-      <c r="D29" s="2">
-        <v>502</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" s="2">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2">
-        <v>1</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:16">
-      <c r="C30" s="2">
-        <v>52002</v>
       </c>
       <c r="D30" s="2">
         <v>502</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M30" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2">
-        <v>1</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="N30" s="5" t="s">
         <v>30</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>141</v>
@@ -3748,7 +3757,7 @@
     </row>
     <row r="31" customHeight="1" spans="3:16">
       <c r="C31" s="2">
-        <v>52003</v>
+        <v>52002</v>
       </c>
       <c r="D31" s="2">
         <v>502</v>
@@ -3775,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>143</v>
@@ -3784,10 +3793,54 @@
         <v>30</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:16">
+      <c r="C32" s="2">
+        <v>52003</v>
+      </c>
+      <c r="D32" s="2">
+        <v>502</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/AchievementConfig.xlsx
+++ b/Excel/AchievementConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="属性奖励" sheetId="1" r:id="rId1"/>
@@ -1792,7 +1792,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2">
         <v>2</v>
@@ -1833,7 +1833,7 @@
         <v>27</v>
       </c>
       <c r="F8" s="2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2">
         <v>3</v>
@@ -1965,7 +1965,7 @@
         <v>41</v>
       </c>
       <c r="F14" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G14" s="2">
         <v>101</v>
@@ -2036,7 +2036,7 @@
         <v>44</v>
       </c>
       <c r="F25" s="2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G25" s="1">
         <v>201</v>
@@ -2075,7 +2075,7 @@
         <v>47</v>
       </c>
       <c r="F26" s="2">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G26" s="1">
         <v>202</v>
@@ -2114,7 +2114,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G27" s="1">
         <v>203</v>
@@ -2153,7 +2153,7 @@
         <v>53</v>
       </c>
       <c r="F28" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G28" s="2">
         <v>204</v>
@@ -2192,7 +2192,7 @@
         <v>56</v>
       </c>
       <c r="F29" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G29" s="2">
         <v>205</v>
@@ -2234,7 +2234,7 @@
         <v>58</v>
       </c>
       <c r="F31" s="2">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="G31" s="2">
         <v>300</v>
@@ -2275,7 +2275,7 @@
         <v>62</v>
       </c>
       <c r="F32" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G32" s="1">
         <v>302</v>
@@ -2316,7 +2316,7 @@
         <v>66</v>
       </c>
       <c r="F33" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G33" s="1">
         <v>303</v>
@@ -2357,7 +2357,7 @@
         <v>69</v>
       </c>
       <c r="F34" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1">
         <v>304</v>
@@ -2398,7 +2398,7 @@
         <v>71</v>
       </c>
       <c r="F35" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G35" s="1">
         <v>305</v>
@@ -2439,7 +2439,7 @@
         <v>73</v>
       </c>
       <c r="F36" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G36" s="1">
         <v>306</v>
@@ -2480,7 +2480,7 @@
         <v>75</v>
       </c>
       <c r="F37" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G37" s="1">
         <v>307</v>
